--- a/data/trans_orig/P16A12-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A12-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>101474</t>
+          <t>98369</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>140457</t>
+          <t>138639</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>146158</t>
+          <t>145202</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>196744</t>
+          <t>192282</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>253011</t>
+          <t>257995</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>317521</t>
+          <t>321433</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,7%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>891266</t>
+          <t>893084</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>930249</t>
+          <t>933354</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1118369</t>
+          <t>1122831</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1168955</t>
+          <t>1169911</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2029314</t>
+          <t>2025402</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2093824</t>
+          <t>2088840</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,01%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41928</t>
+          <t>41046</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68458</t>
+          <t>70096</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19023</t>
+          <t>19722</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40610</t>
+          <t>41385</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64356</t>
+          <t>65742</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>101026</t>
+          <t>101251</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1623936</t>
+          <t>1622298</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1650466</t>
+          <t>1651348</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1547063</t>
+          <t>1546288</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1568650</t>
+          <t>1567951</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3179041</t>
+          <t>3178816</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3215711</t>
+          <t>3214325</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5069</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18922</t>
+          <t>17782</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14974</t>
+          <t>15359</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10971</t>
+          <t>10907</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28022</t>
+          <t>28786</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>532486</t>
+          <t>533626</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>546339</t>
+          <t>546419</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>461438</t>
+          <t>461053</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>473257</t>
+          <t>473488</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>999798</t>
+          <t>999034</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1016849</t>
+          <t>1016913</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>158970</t>
+          <t>159289</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>209442</t>
+          <t>209717</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>177613</t>
+          <t>178922</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>237097</t>
+          <t>234057</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>349023</t>
+          <t>352733</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>424353</t>
+          <t>426803</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3066083</t>
+          <t>3065808</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3116555</t>
+          <t>3116236</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3142100</t>
+          <t>3145140</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3201584</t>
+          <t>3200275</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6230369</t>
+          <t>6227919</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6305699</t>
+          <t>6301989</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,7%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2012 (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>142987</t>
+          <t>144799</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>194416</t>
+          <t>192126</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>212482</t>
+          <t>210756</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>268852</t>
+          <t>268400</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>365823</t>
+          <t>368617</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>440992</t>
+          <t>443021</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,2%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>779412</t>
+          <t>781702</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>830841</t>
+          <t>829029</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1064675</t>
+          <t>1065127</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1121045</t>
+          <t>1122771</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1866363</t>
+          <t>1864334</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1941532</t>
+          <t>1938738</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,02%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55013</t>
+          <t>54306</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87614</t>
+          <t>85967</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39641</t>
+          <t>39087</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69357</t>
+          <t>70545</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>101651</t>
+          <t>101223</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>147637</t>
+          <t>144687</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1872408</t>
+          <t>1874055</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1905009</t>
+          <t>1905716</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1682492</t>
+          <t>1681304</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1712208</t>
+          <t>1712762</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3564234</t>
+          <t>3567184</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3610220</t>
+          <t>3610648</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,27%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>6976</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23626</t>
+          <t>23402</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>2877</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15338</t>
+          <t>14590</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12865</t>
+          <t>12784</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33504</t>
+          <t>32207</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>456706</t>
+          <t>456930</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>472708</t>
+          <t>473356</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>442316</t>
+          <t>443064</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>454896</t>
+          <t>454777</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>904482</t>
+          <t>905779</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>925121</t>
+          <t>925202</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,64%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>218978</t>
+          <t>220005</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>282016</t>
+          <t>281813</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>267696</t>
+          <t>268028</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>336316</t>
+          <t>336282</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>502580</t>
+          <t>503344</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>592217</t>
+          <t>591124</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3132166</t>
+          <t>3132369</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3195204</t>
+          <t>3194177</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3206715</t>
+          <t>3206749</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3275335</t>
+          <t>3275003</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6364996</t>
+          <t>6366089</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6454633</t>
+          <t>6453869</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,77%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>124648</t>
+          <t>124095</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>166157</t>
+          <t>166561</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>160209</t>
+          <t>161950</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>216499</t>
+          <t>213151</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>295393</t>
+          <t>295046</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>369016</t>
+          <t>365229</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,88%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>588190</t>
+          <t>587786</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>629699</t>
+          <t>630252</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>778161</t>
+          <t>781509</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>834451</t>
+          <t>832710</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1379991</t>
+          <t>1383778</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1453614</t>
+          <t>1453961</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,13%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>100140</t>
+          <t>99096</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>141888</t>
+          <t>143668</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64878</t>
+          <t>61941</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>102219</t>
+          <t>100843</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>173057</t>
+          <t>171853</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>230882</t>
+          <t>229870</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1934497</t>
+          <t>1932717</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1976245</t>
+          <t>1977289</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1886081</t>
+          <t>1887457</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1923422</t>
+          <t>1926359</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3833803</t>
+          <t>3834815</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3891628</t>
+          <t>3892832</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12551</t>
+          <t>12529</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31843</t>
+          <t>34259</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>5175</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18008</t>
+          <t>18678</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21156</t>
+          <t>20415</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45684</t>
+          <t>44630</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>515043</t>
+          <t>512627</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>534335</t>
+          <t>534357</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>531132</t>
+          <t>530462</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>544074</t>
+          <t>543965</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1050343</t>
+          <t>1051397</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1074871</t>
+          <t>1075612</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>251885</t>
+          <t>253276</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>315788</t>
+          <t>316025</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>247113</t>
+          <t>244182</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>312817</t>
+          <t>312453</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>513543</t>
+          <t>517992</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>607075</t>
+          <t>609253</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3061830</t>
+          <t>3061593</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3125733</t>
+          <t>3124342</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3219283</t>
+          <t>3219647</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3284987</t>
+          <t>3287918</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6302643</t>
+          <t>6300465</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6396175</t>
+          <t>6391726</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,5%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2023 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>75851</t>
+          <t>76631</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>105153</t>
+          <t>104782</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>138815</t>
+          <t>137302</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>169843</t>
+          <t>168545</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>222230</t>
+          <t>224687</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>264829</t>
+          <t>266937</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,08%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>408789</t>
+          <t>409160</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>438091</t>
+          <t>437311</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>582219</t>
+          <t>583517</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>613247</t>
+          <t>614760</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1001175</t>
+          <t>999067</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1043774</t>
+          <t>1041317</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,25%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>108573</t>
+          <t>103014</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>181687</t>
+          <t>181869</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59589</t>
+          <t>60766</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>101709</t>
+          <t>101355</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>188288</t>
+          <t>184566</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>274566</t>
+          <t>270957</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2108640</t>
+          <t>2108458</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2181754</t>
+          <t>2187313</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2135436</t>
+          <t>2135790</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2177556</t>
+          <t>2176379</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4252906</t>
+          <t>4256515</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4339184</t>
+          <t>4342906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,92%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27659</t>
+          <t>28342</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51211</t>
+          <t>49709</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10893</t>
+          <t>11309</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22552</t>
+          <t>22758</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42398</t>
+          <t>43461</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67421</t>
+          <t>68122</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>595412</t>
+          <t>596914</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>618964</t>
+          <t>618281</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>637911</t>
+          <t>637705</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>649570</t>
+          <t>649154</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1239665</t>
+          <t>1238964</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1264688</t>
+          <t>1263625</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>221870</t>
+          <t>210318</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>321025</t>
+          <t>315810</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>207261</t>
+          <t>206834</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>282209</t>
+          <t>284563</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>464865</t>
+          <t>455554</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>584862</t>
+          <t>580403</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3129867</t>
+          <t>3135082</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3229022</t>
+          <t>3240574</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3367461</t>
+          <t>3365107</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3442409</t>
+          <t>3442836</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6515700</t>
+          <t>6520159</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6635697</t>
+          <t>6645008</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,58%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A12-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A12-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>98369</t>
+          <t>99971</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>138639</t>
+          <t>137841</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>145202</t>
+          <t>145241</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>192282</t>
+          <t>193511</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>257995</t>
+          <t>260118</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>321433</t>
+          <t>321099</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>893084</t>
+          <t>893882</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>933354</t>
+          <t>931752</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1122831</t>
+          <t>1121602</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1169911</t>
+          <t>1169872</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2025402</t>
+          <t>2025736</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2088840</t>
+          <t>2086717</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,92%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41046</t>
+          <t>41062</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70096</t>
+          <t>69736</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19722</t>
+          <t>19507</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41385</t>
+          <t>40342</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>65742</t>
+          <t>68564</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>101251</t>
+          <t>101961</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1622298</t>
+          <t>1622658</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1651348</t>
+          <t>1651332</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1546288</t>
+          <t>1547331</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1567951</t>
+          <t>1568166</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3178816</t>
+          <t>3178106</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3214325</t>
+          <t>3211503</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,91%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17782</t>
+          <t>19626</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2924</t>
+          <t>3193</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15359</t>
+          <t>14742</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10907</t>
+          <t>10192</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28786</t>
+          <t>27411</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>533626</t>
+          <t>531782</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>546419</t>
+          <t>546178</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>461053</t>
+          <t>461670</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>473488</t>
+          <t>473219</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>999034</t>
+          <t>1000409</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1016913</t>
+          <t>1017628</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>159289</t>
+          <t>158228</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>209717</t>
+          <t>209691</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>178922</t>
+          <t>177006</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>234057</t>
+          <t>231537</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>352733</t>
+          <t>352579</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>426803</t>
+          <t>428694</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3065808</t>
+          <t>3065834</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3116236</t>
+          <t>3117297</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3145140</t>
+          <t>3147660</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3200275</t>
+          <t>3202191</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6227919</t>
+          <t>6226028</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6301989</t>
+          <t>6302143</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>144799</t>
+          <t>141856</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>192126</t>
+          <t>193927</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>210756</t>
+          <t>211703</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>268400</t>
+          <t>265884</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>368617</t>
+          <t>370806</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>443021</t>
+          <t>443928</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,24%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>781702</t>
+          <t>779901</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>829029</t>
+          <t>831972</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1065127</t>
+          <t>1067643</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1122771</t>
+          <t>1121824</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1864334</t>
+          <t>1863427</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1938738</t>
+          <t>1936549</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>83,93%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54306</t>
+          <t>55178</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>85967</t>
+          <t>89899</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39087</t>
+          <t>39019</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70545</t>
+          <t>68850</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>101223</t>
+          <t>103014</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>144687</t>
+          <t>146011</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1874055</t>
+          <t>1870123</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1905716</t>
+          <t>1904844</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1681304</t>
+          <t>1682999</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1712762</t>
+          <t>1712830</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3567184</t>
+          <t>3565860</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3610648</t>
+          <t>3608857</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6976</t>
+          <t>7767</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23402</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2877</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14590</t>
+          <t>15582</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12784</t>
+          <t>12286</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32207</t>
+          <t>33210</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>456930</t>
+          <t>455700</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>473356</t>
+          <t>472565</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>443064</t>
+          <t>442072</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>454777</t>
+          <t>454704</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>905779</t>
+          <t>904776</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>925202</t>
+          <t>925700</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>220005</t>
+          <t>218333</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>281813</t>
+          <t>283093</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>268028</t>
+          <t>266373</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>336282</t>
+          <t>333522</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>503344</t>
+          <t>506526</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>591124</t>
+          <t>604961</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3132369</t>
+          <t>3131089</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3194177</t>
+          <t>3195849</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3206749</t>
+          <t>3209509</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3275003</t>
+          <t>3276658</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6366089</t>
+          <t>6352252</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6453869</t>
+          <t>6450687</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,72%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>124095</t>
+          <t>124639</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>166561</t>
+          <t>166102</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>161950</t>
+          <t>161997</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>213151</t>
+          <t>215463</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>295046</t>
+          <t>296015</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>365229</t>
+          <t>366524</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>587786</t>
+          <t>588245</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>630252</t>
+          <t>629708</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>781509</t>
+          <t>779197</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>832710</t>
+          <t>832663</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1383778</t>
+          <t>1382483</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1453961</t>
+          <t>1452992</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,08%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>99096</t>
+          <t>99398</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>143668</t>
+          <t>143082</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61941</t>
+          <t>62919</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>100843</t>
+          <t>101797</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>171853</t>
+          <t>173955</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>229870</t>
+          <t>229699</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1932717</t>
+          <t>1933303</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1977289</t>
+          <t>1976987</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1887457</t>
+          <t>1886503</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1926359</t>
+          <t>1925381</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3834815</t>
+          <t>3834986</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3892832</t>
+          <t>3890730</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12529</t>
+          <t>12799</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34259</t>
+          <t>34562</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5175</t>
+          <t>5069</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18678</t>
+          <t>17863</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20415</t>
+          <t>20791</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44630</t>
+          <t>45778</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>512627</t>
+          <t>512324</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>534357</t>
+          <t>534087</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>530462</t>
+          <t>531277</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>543965</t>
+          <t>544071</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1051397</t>
+          <t>1050249</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1075612</t>
+          <t>1075236</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>253276</t>
+          <t>253846</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>316025</t>
+          <t>319248</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>244182</t>
+          <t>245523</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>312453</t>
+          <t>311844</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>517992</t>
+          <t>517395</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>609253</t>
+          <t>612275</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3061593</t>
+          <t>3058370</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3124342</t>
+          <t>3123772</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3219647</t>
+          <t>3220256</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3287918</t>
+          <t>3286577</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6300465</t>
+          <t>6297443</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6391726</t>
+          <t>6392323</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,51%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>90663</t>
+          <t>96667</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>76631</t>
+          <t>82810</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>104782</t>
+          <t>111956</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>152968</t>
+          <t>164876</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>137302</t>
+          <t>147321</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>168545</t>
+          <t>182056</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>243631</t>
+          <t>261543</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>224687</t>
+          <t>238553</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>266937</t>
+          <t>286640</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>423279</t>
+          <t>480875</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>409160</t>
+          <t>465586</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>437311</t>
+          <t>494732</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>599094</t>
+          <t>655240</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>583517</t>
+          <t>638060</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>614760</t>
+          <t>672795</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1022373</t>
+          <t>1136115</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>999067</t>
+          <t>1111018</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1041317</t>
+          <t>1159105</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,93%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>752062</t>
+          <t>820116</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>752062</t>
+          <t>820116</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>752062</t>
+          <t>820116</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1266004</t>
+          <t>1397658</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1266004</t>
+          <t>1397658</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1266004</t>
+          <t>1397658</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>153186</t>
+          <t>166215</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>103014</t>
+          <t>143643</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>181869</t>
+          <t>190717</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>84091</t>
+          <t>93009</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60766</t>
+          <t>80610</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>101355</t>
+          <t>108259</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>237277</t>
+          <t>259224</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>184566</t>
+          <t>236184</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>270957</t>
+          <t>287412</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2137141</t>
+          <t>2064351</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2108458</t>
+          <t>2039849</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2187313</t>
+          <t>2086923</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2153054</t>
+          <t>2077698</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2135790</t>
+          <t>2062448</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2176379</t>
+          <t>2090097</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4290195</t>
+          <t>4142050</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4256515</t>
+          <t>4113862</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4342906</t>
+          <t>4165090</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>94,63%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>37627</t>
+          <t>42666</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28342</t>
+          <t>32200</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49709</t>
+          <t>56907</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>16068</t>
+          <t>18693</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11309</t>
+          <t>12835</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22758</t>
+          <t>26656</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>53695</t>
+          <t>61358</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43461</t>
+          <t>48959</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68122</t>
+          <t>75448</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>608996</t>
+          <t>668921</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>596914</t>
+          <t>654680</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>618281</t>
+          <t>679387</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>644395</t>
+          <t>716184</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>637705</t>
+          <t>708221</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>649154</t>
+          <t>722042</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1253391</t>
+          <t>1385106</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1238964</t>
+          <t>1371016</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1263625</t>
+          <t>1397505</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,69 +6566,69 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>281476</t>
+          <t>305547</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>210318</t>
+          <t>276139</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>315810</t>
+          <t>336721</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>8,68%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,85%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,57%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>276577</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>255348</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>303876</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>7,42%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>6,85%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
           <t>8,16%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,09%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,15%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>521</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>253127</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>206834</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>284563</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>6,94%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>5,67%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>7,8%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>925</t>
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>534603</t>
+          <t>582125</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>455554</t>
+          <t>546067</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>580403</t>
+          <t>621196</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -6679,67 +6679,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3169416</t>
+          <t>3214148</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3135082</t>
+          <t>3182974</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3240574</t>
+          <t>3243556</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>91,32%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,43%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92,15%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>4827</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>3449124</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>3421825</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3470353</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>92,58%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
           <t>91,84%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>90,85%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,91%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>4827</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>3396543</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>3365107</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3442836</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>93,06%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>92,2%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6565959</t>
+          <t>6663271</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6520159</t>
+          <t>6624200</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6645008</t>
+          <t>6699329</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>92,46%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3450892</t>
+          <t>3519695</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3450892</t>
+          <t>3519695</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3450892</t>
+          <t>3519695</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3649670</t>
+          <t>3725701</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3649670</t>
+          <t>3725701</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3649670</t>
+          <t>3725701</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7100562</t>
+          <t>7245396</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7100562</t>
+          <t>7245396</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7100562</t>
+          <t>7245396</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
